--- a/website_content_creation/authors/Isabel_DaCunhaJuchem/Copy of Author_form.xlsx
+++ b/website_content_creation/authors/Isabel_DaCunhaJuchem/Copy of Author_form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esmender\OneDrive - NRCan RNCan\Documents\WET lab\GLFC-WET.github.io\website_content_creation\authors\Isabel_DaCunhaJuchem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://041gc-my.sharepoint.com/personal/emily_smenderovac_nrcan-rncan_gc_ca/Documents/Documents/WET lab/GLFC-WET.github.io/website_content_creation/authors/Isabel_DaCunhaJuchem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCB5380-1A8D-4C5E-A69B-53848EF38067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4CCB5380-1A8D-4C5E-A69B-53848EF38067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BCF1FAA-83DB-48A1-B523-725216973A6B}"/>
   <bookViews>
-    <workbookView xWindow="-9315" yWindow="-13875" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14235" yWindow="-16395" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,9 +147,6 @@
     <t>PosGraduate Cert. in Microbiology, Fundamentals and Biotechnology</t>
   </si>
   <si>
-    <t>Watershed Ecology Team</t>
-  </si>
-  <si>
     <t>Great Lakes Forestry Centre</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>Watershed Analyst</t>
+  </si>
+  <si>
+    <t>Past WETlab Members</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -947,7 +947,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="33" t="s">
         <v>41</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
